--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486483_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486483_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.0319</v>
+        <v>1.4597</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9235</v>
+        <v>2.2588</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8915999999999999</v>
+        <v>-0.7991</v>
       </c>
       <c r="G2" t="n">
         <v>1.1572</v>
@@ -610,13 +610,13 @@
         <v>1.9576</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.5414</v>
+        <v>-1.1137</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3014</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.24</v>
+        <v>-0.1475</v>
       </c>
       <c r="V2" t="n">
         <v>1.8511</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9169</v>
+        <v>1.4372</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1784</v>
+        <v>2.5137</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.2615</v>
+        <v>-1.0765</v>
       </c>
       <c r="G3" t="n">
         <v>2.3705</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.0448</v>
+        <v>-0.5245</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.3377</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3718</v>
+        <v>-0.1869</v>
       </c>
       <c r="V3" t="n">
         <v>-0.4088</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>O. SIQUIER COSTA</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0129</v>
+        <v>-0.2369</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.1571</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0129</v>
+        <v>-0.394</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7785</v>
+        <v>0.7931</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9275</v>
+        <v>2.1717</v>
       </c>
       <c r="I4" t="n">
-        <v>0.149</v>
+        <v>-1.3786</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.7451</v>
+        <v>2.3177</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.7451</v>
+        <v>2.1264</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1912</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0335</v>
+        <v>-1.5246</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1825</v>
+        <v>0.0452</v>
       </c>
       <c r="O4" t="n">
-        <v>0.149</v>
+        <v>-1.5698</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7655999999999999</v>
+        <v>-0.2938</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7451</v>
+        <v>-0.7234</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0205</v>
+        <v>0.4296</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3514</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.604</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>O. SIQUIER COSTA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1522</v>
+        <v>-0.4291</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0664</v>
+        <v>-0.447</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0858</v>
+        <v>0.0179</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7931</v>
+        <v>-0.7785</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1717</v>
+        <v>-0.9275</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3786</v>
+        <v>0.149</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3177</v>
+        <v>-0.7451</v>
       </c>
       <c r="K5" t="n">
-        <v>2.1264</v>
+        <v>-0.7451</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1912</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5246</v>
+        <v>-0.0335</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0452</v>
+        <v>-0.1825</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.5698</v>
+        <v>0.149</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2091</v>
+        <v>0.3494</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9469</v>
+        <v>0.298</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7378</v>
+        <v>0.0514</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3514</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5009</v>
+        <v>-1.971</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.6272</v>
+        <v>-2.8507</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1264</v>
+        <v>0.8798</v>
       </c>
       <c r="G6" t="n">
         <v>0.2466</v>
@@ -922,13 +922,13 @@
         <v>0.6525</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1661</v>
+        <v>-0.304</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3509</v>
+        <v>-0.5744</v>
       </c>
       <c r="U6" t="n">
-        <v>0.517</v>
+        <v>0.2704</v>
       </c>
       <c r="V6" t="n">
         <v>0.9141</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>A. SCARIOLO ARES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9186</v>
+        <v>-2.1003</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1244</v>
+        <v>-1.5116</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.7942</v>
+        <v>-0.5888</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.362</v>
+        <v>0.0264</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.2798</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7204</v>
+        <v>-0.2534</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5538</v>
+        <v>0.8942</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5538</v>
+        <v>0.8942</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9158</v>
+        <v>-0.8679</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1954</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7204</v>
+        <v>-0.2534</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.305</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q7" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R7" t="n">
-        <v>0.87</v>
+        <v>0.435</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1834</v>
+        <v>-0.3866</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7367</v>
+        <v>-0.2307</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5533</v>
+        <v>-0.1559</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5649999999999999</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0039</v>
+        <v>-2.1851</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.4108</v>
+        <v>-0.7461</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5931</v>
+        <v>-1.439</v>
       </c>
       <c r="G8" t="n">
         <v>-0.9322</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0583</v>
+        <v>-0.1229</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4026</v>
+        <v>0.0673</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3443</v>
+        <v>-0.1902</v>
       </c>
       <c r="V8" t="n">
         <v>-1.13</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SCARIOLO ARES</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1813</v>
+        <v>-2.4042</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6233</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5579</v>
+        <v>-1.6093</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0264</v>
+        <v>-1.362</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2798</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2534</v>
+        <v>-0.7204</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8942</v>
+        <v>0.5538</v>
       </c>
       <c r="K9" t="n">
-        <v>0.8942</v>
+        <v>0.5538</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8679</v>
+        <v>-1.9158</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.1954</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2534</v>
+        <v>-0.7204</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7401</v>
+        <v>-1.305</v>
       </c>
       <c r="Q9" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4676</v>
+        <v>-0.3022</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3425</v>
+        <v>0.06610000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1251</v>
+        <v>-0.3683</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5343</v>
+        <v>-3.0564</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.5858</v>
+        <v>-1.1388</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9485</v>
+        <v>-1.9176</v>
       </c>
       <c r="G10" t="n">
         <v>-2.5825</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0225</v>
+        <v>-0.5447</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.2944</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2811</v>
+        <v>-0.2503</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7993</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7901</v>
+        <v>-5.6745</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.738</v>
+        <v>-2.9615</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0521</v>
+        <v>-2.713</v>
       </c>
       <c r="G11" t="n">
         <v>-4.2937</v>
@@ -1312,13 +1312,13 @@
         <v>1.5225</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5839</v>
+        <v>-0.4684</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3389</v>
+        <v>-0.5624</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.245</v>
+        <v>0.094</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.9498</v>
+        <v>-5.9343</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0818</v>
+        <v>-4.6348</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.8679</v>
+        <v>-1.2994</v>
       </c>
       <c r="G12" t="n">
         <v>-5.4742</v>
@@ -1390,13 +1390,13 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3718</v>
+        <v>-0.3563</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2209</v>
+        <v>-0.7739</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8491</v>
+        <v>0.4176</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9738</v>
@@ -1423,25 +1423,25 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-21.0952</v>
+        <v>-21.0949</v>
       </c>
       <c r="E13" t="n">
         <v>-10.1558</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.9391</v>
+        <v>-10.939</v>
       </c>
       <c r="G13" t="n">
         <v>-10.8293</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7451000000000001</v>
+        <v>0.7451000000000005</v>
       </c>
       <c r="I13" t="n">
         <v>-11.5745</v>
       </c>
       <c r="J13" t="n">
-        <v>5.6274</v>
+        <v>5.627399999999998</v>
       </c>
       <c r="K13" t="n">
         <v>5.7508</v>
@@ -1468,13 +1468,13 @@
         <v>10.8752</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.0677</v>
+        <v>-4.067699999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.031400000000001</v>
+        <v>-4.0317</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.03620000000000012</v>
+        <v>-0.03610000000000008</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7603000000000002</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. FAURE RIBES</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.0763</v>
+        <v>6.9833</v>
       </c>
       <c r="E14" t="n">
-        <v>6.6211</v>
+        <v>5.0224</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4553</v>
+        <v>1.961</v>
       </c>
       <c r="G14" t="n">
-        <v>4.1317</v>
+        <v>6.6661</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5666</v>
+        <v>2.2937</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5651</v>
+        <v>4.3724</v>
       </c>
       <c r="J14" t="n">
-        <v>4.9184</v>
+        <v>7.8887</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9294</v>
+        <v>2.6469</v>
       </c>
       <c r="L14" t="n">
-        <v>1.989</v>
+        <v>5.2418</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.7867</v>
+        <v>-1.2226</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.3628</v>
+        <v>-0.3532</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5760999999999999</v>
+        <v>-0.8694</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.5225</v>
+        <v>-3.6976</v>
       </c>
       <c r="R14" t="n">
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>3.5967</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>2.8348</v>
+        <v>-0.4939</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7619</v>
+        <v>1.0085</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.3045</v>
+        <v>1.3252</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3904</v>
+        <v>1.3252</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.0588</v>
+        <v>6.3215</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2107</v>
+        <v>4.5402</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8481</v>
+        <v>1.7814</v>
       </c>
       <c r="G15" t="n">
         <v>2.2298</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6767</v>
+        <v>0.9394</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7487</v>
+        <v>0.0781</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9281</v>
+        <v>0.8613</v>
       </c>
       <c r="V15" t="n">
         <v>2.0647</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>A. FAURE RIBES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3179</v>
+        <v>4.7565</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3518</v>
+        <v>4.6094</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9661</v>
+        <v>0.147</v>
       </c>
       <c r="G16" t="n">
-        <v>6.6661</v>
+        <v>4.1317</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2937</v>
+        <v>1.5666</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3724</v>
+        <v>2.5651</v>
       </c>
       <c r="J16" t="n">
-        <v>7.8887</v>
+        <v>4.9184</v>
       </c>
       <c r="K16" t="n">
-        <v>2.6469</v>
+        <v>2.9294</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2418</v>
+        <v>1.989</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2226</v>
+        <v>-0.7867</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3532</v>
+        <v>-1.3628</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.8694</v>
+        <v>0.5760999999999999</v>
       </c>
       <c r="P16" t="n">
+        <v>0.6525</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-1.5225</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-3.6976</v>
       </c>
       <c r="R16" t="n">
         <v>2.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1508</v>
+        <v>1.2768</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1644</v>
+        <v>0.8232</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0136</v>
+        <v>0.4536</v>
       </c>
       <c r="V16" t="n">
-        <v>1.3252</v>
+        <v>-1.3045</v>
       </c>
       <c r="W16" t="n">
-        <v>1.3252</v>
+        <v>0.3904</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.695</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4764</v>
+        <v>2.4533</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1998</v>
+        <v>0.4233</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2766</v>
+        <v>2.03</v>
       </c>
       <c r="G17" t="n">
         <v>0.125</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8066</v>
+        <v>0.7835</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1454</v>
+        <v>0.0781</v>
       </c>
       <c r="U17" t="n">
-        <v>0.952</v>
+        <v>0.7054</v>
       </c>
       <c r="V17" t="n">
         <v>-0.1952</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7302</v>
+        <v>0.9601</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.3751</v>
+        <v>-1.2633</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1053</v>
+        <v>2.2234</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9514</v>
@@ -1858,13 +1858,13 @@
         <v>2.1751</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2895</v>
+        <v>0.5194</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2704</v>
+        <v>-0.1586</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5599</v>
+        <v>0.678</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>F. COPES</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0929</v>
+        <v>0.4774</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2495</v>
+        <v>-1.0218</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1566</v>
+        <v>1.4991</v>
       </c>
       <c r="G19" t="n">
-        <v>0.152</v>
+        <v>-0.6307</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.146</v>
+        <v>-1.9009</v>
       </c>
       <c r="I19" t="n">
-        <v>0.298</v>
+        <v>1.2702</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0365</v>
+        <v>-0.044</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0365</v>
+        <v>-0.5046</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.4606</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1155</v>
+        <v>-0.5867</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1825</v>
+        <v>-1.3963</v>
       </c>
       <c r="O19" t="n">
-        <v>0.298</v>
+        <v>0.8096</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2175</v>
+        <v>0.435</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.7401</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0274</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.06850000000000001</v>
+        <v>-0.2584</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0411</v>
+        <v>0.3458</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4895</v>
+        <v>0.2248</v>
       </c>
       <c r="E20" t="n">
-        <v>0.228</v>
+        <v>0.0975</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.7175</v>
+        <v>0.1273</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4642</v>
+        <v>-0.7026</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2833</v>
+        <v>-1.3322</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8192</v>
+        <v>0.6296</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1185</v>
+        <v>-0.4993</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0037</v>
+        <v>-0.6173</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1147</v>
+        <v>0.118</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6543</v>
+        <v>-0.2033</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2796</v>
+        <v>-0.7149</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9339</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="Q20" t="n">
         <v>-0.2175</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>-1.305</v>
       </c>
       <c r="R20" t="n">
         <v>1.0875</v>
       </c>
       <c r="S20" t="n">
-        <v>0.024</v>
+        <v>0.0574</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4146</v>
+        <v>0.0541</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3906</v>
+        <v>0.0033</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.7602</v>
       </c>
       <c r="X20" t="n">
         <v>-0.7602</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>F. COPES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5708</v>
+        <v>-0.0312</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.9158</v>
+        <v>-0.2495</v>
       </c>
       <c r="F21" t="n">
-        <v>1.345</v>
+        <v>0.2183</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6307</v>
+        <v>0.152</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.9009</v>
+        <v>-0.146</v>
       </c>
       <c r="I21" t="n">
-        <v>1.2702</v>
+        <v>0.298</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.044</v>
+        <v>0.0365</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5046</v>
+        <v>0.0365</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4606</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5867</v>
+        <v>0.1155</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3963</v>
+        <v>-0.1825</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8096</v>
+        <v>0.298</v>
       </c>
       <c r="P21" t="n">
-        <v>0.435</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="R21" t="n">
-        <v>1.7401</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9608</v>
+        <v>0.0342</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1524</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1917</v>
+        <v>0.1027</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5999</v>
+        <v>-0.144</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5731000000000001</v>
+        <v>0.1163</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0268</v>
+        <v>-0.2603</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.7026</v>
+        <v>0.4642</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.3322</v>
+        <v>1.2833</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6296</v>
+        <v>-0.8192</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4993</v>
+        <v>1.1185</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6173</v>
+        <v>1.0037</v>
       </c>
       <c r="L22" t="n">
-        <v>0.118</v>
+        <v>0.1147</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2033</v>
+        <v>-0.6543</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.7149</v>
+        <v>0.2796</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.9339</v>
       </c>
       <c r="P22" t="n">
-        <v>0.87</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="R22" t="n">
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7673</v>
+        <v>0.3695</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6165</v>
+        <v>0.3028</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1508</v>
+        <v>0.0667</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W22" t="n">
-        <v>0.7602</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>-0.7602</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.8115</v>
+        <v>-0.1616</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5588</v>
+        <v>-1.3353</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7473</v>
+        <v>1.1737</v>
       </c>
       <c r="G23" t="n">
         <v>-0.6546</v>
@@ -2248,13 +2248,13 @@
         <v>2.3926</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4195</v>
+        <v>0.2304</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5444</v>
+        <v>-0.3208</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1248</v>
+        <v>0.5513</v>
       </c>
       <c r="V23" t="n">
         <v>-1.695</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.095</v>
+        <v>21.8401</v>
       </c>
       <c r="E24" t="n">
-        <v>10.9391</v>
+        <v>10.9392</v>
       </c>
       <c r="F24" t="n">
-        <v>10.156</v>
+        <v>10.9009</v>
       </c>
       <c r="G24" t="n">
         <v>10.8295</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7450000000000001</v>
+        <v>-0.7449999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>11.5745</v>
@@ -2302,7 +2302,7 @@
         <v>16.4569</v>
       </c>
       <c r="K24" t="n">
-        <v>5.005799999999999</v>
+        <v>5.005800000000001</v>
       </c>
       <c r="L24" t="n">
         <v>11.4511</v>
@@ -2311,10 +2311,10 @@
         <v>-5.6274</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.7507</v>
+        <v>-5.750699999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1234000000000001</v>
+        <v>0.1234000000000002</v>
       </c>
       <c r="P24" t="n">
         <v>5.4377</v>
@@ -2326,19 +2326,19 @@
         <v>16.3131</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0677</v>
+        <v>4.812600000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0360999999999998</v>
+        <v>0.03609999999999997</v>
       </c>
       <c r="U24" t="n">
-        <v>4.0317</v>
+        <v>4.7766</v>
       </c>
       <c r="V24" t="n">
-        <v>0.7602</v>
+        <v>0.7601999999999995</v>
       </c>
       <c r="W24" t="n">
-        <v>5.321400000000001</v>
+        <v>5.3214</v>
       </c>
       <c r="X24" t="n">
         <v>-4.5613</v>
